--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137131834</v>
+        <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Flakamyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712170</v>
+        <v>712242</v>
       </c>
       <c r="R2" t="n">
-        <v>7196795</v>
+        <v>7196798</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,92 +755,90 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131834</t>
+          <t>https://artportalen.se/Sighting/137149732</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137131835</v>
+        <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>92091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Flakamyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712173</v>
+        <v>712242</v>
       </c>
       <c r="R3" t="n">
-        <v>7196795</v>
+        <v>7196798</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,92 +865,90 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131835</t>
+          <t>https://artportalen.se/Sighting/137149736</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137131838</v>
+        <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Storkölmyrbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712251</v>
+        <v>712291</v>
       </c>
       <c r="R4" t="n">
         <v>7196618</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,54 +975,45 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131838</t>
+          <t>https://artportalen.se/Sighting/137149784</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137131839</v>
+        <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712215</v>
+        <v>712170</v>
       </c>
       <c r="R5" t="n">
-        <v>7196594</v>
+        <v>7196795</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,62 +1116,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131839</t>
+          <t>https://artportalen.se/Sighting/137131834</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137131837</v>
+        <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712253</v>
+        <v>712173</v>
       </c>
       <c r="R6" t="n">
-        <v>7196799</v>
+        <v>7196795</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,12 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,59 +1228,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131837</t>
+          <t>https://artportalen.se/Sighting/137131835</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137131840</v>
+        <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712174</v>
+        <v>712251</v>
       </c>
       <c r="R7" t="n">
-        <v>7196569</v>
+        <v>7196618</v>
       </c>
       <c r="S7" t="n">
         <v>13</v>
@@ -1331,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observerad</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,16 +1325,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Översvämmad bäckmiljö</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,7 +1340,1399 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137131838</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137131839</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>712215</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7196594</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131839</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137149698</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>712231</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7196794</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149698</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137149744</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>712304</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7196692</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149744</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137149782</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storkölmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>712291</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7196618</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>rik förekomst</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149782</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137149786</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storkölmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>712249</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7196623</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149786</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137131837</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>712253</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7196799</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131837</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137149693</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>712216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7196792</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149693</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137131840</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>712174</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7196569</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Översvämmad bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137131840</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137149676</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>712191</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7196784</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149676</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137149688</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>712216</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7196792</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149688</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137149767</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>712305</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7196656</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149767</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137149795</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storkölmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>712181</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7196575</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149795</t>
         </is>
       </c>
     </row>
@@ -1394,6 +2744,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,56 +1903,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137131837</v>
+        <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712253</v>
+        <v>712139</v>
       </c>
       <c r="R13" t="n">
-        <v>7196799</v>
+        <v>7196791</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,7 +1973,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,12 +1983,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,73 +1998,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131837</t>
+          <t>https://artportalen.se/Sighting/137233949</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137149693</v>
+        <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flakamyran, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712216</v>
+        <v>712357</v>
       </c>
       <c r="R14" t="n">
-        <v>7196792</v>
+        <v>7196746</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,14 +2083,19 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack på gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,70 +2110,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149693</t>
+          <t>https://artportalen.se/Sighting/137233951</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137131840</v>
+        <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712174</v>
+        <v>712290</v>
       </c>
       <c r="R15" t="n">
-        <v>7196569</v>
+        <v>7196625</v>
       </c>
       <c r="S15" t="n">
         <v>13</v>
@@ -2221,7 +2197,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,12 +2207,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Observerad</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,87 +2218,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Översvämmad bäckmiljö</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131840</t>
+          <t>https://artportalen.se/Sighting/137233953</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137149676</v>
+        <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flakamyran, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712191</v>
+        <v>712224</v>
       </c>
       <c r="R16" t="n">
-        <v>7196784</v>
+        <v>7196604</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,21 +2307,26 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2376,73 +2334,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149676</t>
+          <t>https://artportalen.se/Sighting/137233954</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137149688</v>
+        <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flakamyran, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712216</v>
+        <v>712167</v>
       </c>
       <c r="R17" t="n">
-        <v>7196792</v>
+        <v>7196568</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,21 +2419,26 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2491,44 +2446,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149688</t>
+          <t>https://artportalen.se/Sighting/137233955</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137149767</v>
+        <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2547,17 +2502,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flakamyran, Vb</t>
+          <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712305</v>
+        <v>712253</v>
       </c>
       <c r="R18" t="n">
-        <v>7196656</v>
+        <v>7196799</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2584,21 +2539,31 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2606,44 +2571,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149767</t>
+          <t>https://artportalen.se/Sighting/137131837</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137149795</v>
+        <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2662,14 +2627,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storkölmyrbäcken, Vb</t>
+          <t>Flakamyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712181</v>
+        <v>712216</v>
       </c>
       <c r="R19" t="n">
-        <v>7196575</v>
+        <v>7196792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,14 +2671,14 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2731,6 +2696,718 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149693</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137233952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58018</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>712289</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7196693</v>
+      </c>
+      <c r="S20" t="n">
+        <v>31</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rotsockelhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137233952</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137131840</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>712174</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7196569</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Översvämmad bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131840</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137149676</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>712191</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7196784</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149676</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137149688</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>712216</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7196792</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149688</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137149767</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flakamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>712305</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7196656</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137149767</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137149795</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storkölmyrbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>712181</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7196575</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137149795</t>
         </is>
@@ -2756,6 +3433,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137233952</v>
       </c>
       <c r="B20" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137131840</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137149676</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>137149688</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>137149767</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>137149795</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -2494,11 +2494,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2619,11 +2615,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2851,11 +2843,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2986,11 +2974,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3101,11 +3085,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3216,11 +3196,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3331,11 +3307,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137233952</v>
       </c>
       <c r="B20" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137131840</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>137149676</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137149688</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>137149767</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>137149795</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137233952</v>
       </c>
       <c r="B20" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137131840</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>137149676</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137149688</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>137149767</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>137149795</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137233952</v>
       </c>
       <c r="B20" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137131840</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>137149676</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137149688</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>137149767</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>137149795</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 38222-2026 artfynd.xlsx
+++ b/artfynd/A 38222-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149732</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137149736</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137149784</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137131834</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137131835</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131838</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137131839</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137149698</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137149744</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>137149782</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137149786</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137233949</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137233951</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>137233953</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>137233954</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>137233955</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137131837</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137149693</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>137233952</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>137131840</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>137149676</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137149688</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>137149767</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>137149795</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
